--- a/week-04/Market position.xlsx
+++ b/week-04/Market position.xlsx
@@ -15,7 +15,20 @@
   <sheets>
     <sheet name="data-1777485576254" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -659,6 +672,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-B323-4CF5-B63B-F858641BE20E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -674,6 +692,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-B323-4CF5-B63B-F858641BE20E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>

--- a/week-04/Market position.xlsx
+++ b/week-04/Market position.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\onurkaraer\Documents\DataAnalytics\week-04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE47204-B65A-4AAC-88CA-C9B79941E43A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC0EA86-50D2-4EEA-AD2D-86354949B76B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0227B73C-B077-46DC-8974-EDB1B12BED6C}"/>
   </bookViews>
   <sheets>
     <sheet name="data-1777485576254" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,15 +33,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>vendor_group</t>
   </si>
   <si>
     <t>total_revenue</t>
-  </si>
-  <si>
-    <t>market_share_pct</t>
   </si>
   <si>
     <t>Bacardi</t>
@@ -1745,7 +1742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7E57260-AF33-445C-869C-D79D47827CA8}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -1753,37 +1750,28 @@
     <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
       </c>
       <c r="B2" s="1">
         <v>21216356.719999999</v>
       </c>
-      <c r="C2">
-        <v>5.41</v>
-      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1">
         <v>371076666.88999999</v>
-      </c>
-      <c r="C3">
-        <v>94.59</v>
       </c>
     </row>
   </sheetData>
